--- a/volatilidad_ddewma.xlsx
+++ b/volatilidad_ddewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-27</t>
   </si>
 </sst>
 </file>
@@ -584,6 +587,17 @@
         <v>0.0228961127436084</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.000475001465635433</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0217945283416603</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/volatilidad_ddewma.xlsx
+++ b/volatilidad_ddewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-28</t>
   </si>
 </sst>
 </file>
@@ -598,6 +601,17 @@
         <v>0.0217945283416603</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.000512468980009489</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.022637777717998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/volatilidad_ddewma.xlsx
+++ b/volatilidad_ddewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-29</t>
   </si>
 </sst>
 </file>
@@ -612,6 +615,17 @@
         <v>0.022637777717998</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.000470092606064584</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0216816190830986</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/volatilidad_ddewma.xlsx
+++ b/volatilidad_ddewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-30</t>
   </si>
 </sst>
 </file>
@@ -626,6 +629,17 @@
         <v>0.0216816190830986</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.000419115894854463</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0204723202117997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
